--- a/Config/DialogueGroupConfig.xlsx
+++ b/Config/DialogueGroupConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16725" windowHeight="10200"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -64,169 +64,169 @@
     <t>怪物Id(1001~1005普通,2001Boss,3001精英)</t>
   </si>
   <si>
-    <t>玩家台词(玩家先说,&lt;=20字)</t>
-  </si>
-  <si>
-    <t>怪物台词(回应玩家,&lt;=20字)</t>
-  </si>
-  <si>
-    <t>就你这团黏液,也敢拦路?</t>
+    <t>玩家台词(回应怪物,&lt;=20字)</t>
+  </si>
+  <si>
+    <t>怪物台词(怪物先说,&lt;=20字)</t>
+  </si>
+  <si>
+    <t>黏液?一巴掌拍扁你!</t>
+  </si>
+  <si>
+    <t>站住,先尝尝我的黏液!</t>
+  </si>
+  <si>
+    <t>正好,省得你逃跑!</t>
   </si>
   <si>
     <t>黏住你,你就走不掉啦!</t>
   </si>
   <si>
-    <t>一巴掌就能拍扁你。</t>
-  </si>
-  <si>
-    <t>拍扁之前,先尝尝黏液!</t>
-  </si>
-  <si>
-    <t>软趴趴的,拿什么跟我打?</t>
+    <t>赢我?先扛住这一巴掌!</t>
   </si>
   <si>
     <t>软归软,黏住你就赢了!</t>
   </si>
   <si>
-    <t>小家伙,你挡着我发财了。</t>
-  </si>
-  <si>
-    <t>那我把你粘成金币模样!</t>
-  </si>
-  <si>
-    <t>狼哥,看完电影又来拦路?</t>
-  </si>
-  <si>
-    <t>学了发哥几手,试试吧!</t>
-  </si>
-  <si>
-    <t>你也会玩炸金花?</t>
+    <t>那我发财就指望你了。</t>
+  </si>
+  <si>
+    <t>我要把你粘成金币模样!</t>
+  </si>
+  <si>
+    <t>试试就试试,亮牌!</t>
+  </si>
+  <si>
+    <t>学了发哥几手,来试试!</t>
+  </si>
+  <si>
+    <t>看片归看片,打牌归打牌!</t>
   </si>
   <si>
     <t>港片看多了,牌技自然有!</t>
   </si>
   <si>
-    <t>亮牌吧,别整慢动作。</t>
+    <t>气场再足,不如牌好。</t>
   </si>
   <si>
     <t>压牌这一手,叫气场!</t>
   </si>
   <si>
-    <t>你是赌神,我是赌侠。</t>
-  </si>
-  <si>
-    <t>那就比比谁的底牌硬!</t>
-  </si>
-  <si>
-    <t>呱呱叫的,你也想亮牌?</t>
+    <t>正合我意,赌神驾到!</t>
+  </si>
+  <si>
+    <t>比比谁的底牌更硬!</t>
+  </si>
+  <si>
+    <t>翻盘也得问过我的牌!</t>
   </si>
   <si>
     <t>总被忽视,今天我翻盘!</t>
   </si>
   <si>
-    <t>就凭你?省省吧。</t>
+    <t>那今天让你输个明白。</t>
   </si>
   <si>
     <t>翻身仗,我可没输过!</t>
   </si>
   <si>
-    <t>你的牌和你一样瘪。</t>
+    <t>口气不小,牌桌上见!</t>
   </si>
   <si>
     <t>瘪牌正好压你一头!</t>
   </si>
   <si>
-    <t>小青蛙也配上桌?</t>
+    <t>行,先让你叫两声。</t>
   </si>
   <si>
     <t>上桌才轮到我呱呱叫!</t>
   </si>
   <si>
-    <t>嗡嗡嗡,吵死了!</t>
-  </si>
-  <si>
-    <t>吵到你手抖,嘿嘿!</t>
-  </si>
-  <si>
-    <t>你这伤害,挠痒都不够。</t>
+    <t>手抖也比你动听。</t>
+  </si>
+  <si>
+    <t>嗡嗡嗡,吵到你手抖!</t>
+  </si>
+  <si>
+    <t>先把你自个儿烦哭吧。</t>
   </si>
   <si>
     <t>烦也能把你烦输!</t>
   </si>
   <si>
-    <t>蜜蜂快回花丛去。</t>
+    <t>好玩也留不住你赢牌。</t>
   </si>
   <si>
     <t>花丛哪有牌桌好玩!</t>
   </si>
   <si>
-    <t>蜜蜂也会玩牌?</t>
+    <t>先赢我一局再开嗓。</t>
   </si>
   <si>
     <t>我还能唱着歌赢你!</t>
   </si>
   <si>
-    <t>走得慢,出牌也慢?</t>
-  </si>
-  <si>
-    <t>慢工出细活,稳赢!</t>
-  </si>
-  <si>
-    <t>你这身板,挺抗揍啊。</t>
+    <t>稳不稳,亮牌才知道。</t>
+  </si>
+  <si>
+    <t>慢工出细活,这把稳赢!</t>
+  </si>
+  <si>
+    <t>来吧,让我看看你多壮。</t>
   </si>
   <si>
     <t>先扛过我这一把再说!</t>
   </si>
   <si>
-    <t>蘑菇人,让个路。</t>
+    <t>拳头再硬,硬不过好牌。</t>
   </si>
   <si>
     <t>路没有,拳头有一把!</t>
   </si>
   <si>
-    <t>看你老实,让你先出。</t>
+    <t>嘴上赢了,牌还没出呢。</t>
   </si>
   <si>
     <t>慢是慢,赢你足够了!</t>
   </si>
   <si>
-    <t>又来一只蘑菇?</t>
-  </si>
-  <si>
-    <t>进化体,可不好惹!</t>
-  </si>
-  <si>
-    <t>进化了就能赢我?</t>
-  </si>
-  <si>
-    <t>这把让你见识一下!</t>
-  </si>
-  <si>
-    <t>你兄弟刚被我揍过。</t>
-  </si>
-  <si>
-    <t>所以我来讨回场子!</t>
-  </si>
-  <si>
-    <t>大眼仔,你死期到了。</t>
-  </si>
-  <si>
-    <t>瞪大眼,看谁输谁赢!</t>
-  </si>
-  <si>
-    <t>一路杀到你面前了。</t>
+    <t>好惹不好惹,亮牌见!</t>
+  </si>
+  <si>
+    <t>进化体,可不是好惹的!</t>
+  </si>
+  <si>
+    <t>见识过了,不过如此。</t>
+  </si>
+  <si>
+    <t>这把让你见识进化!</t>
+  </si>
+  <si>
+    <t>先问问我的牌答不答应。</t>
+  </si>
+  <si>
+    <t>我来替兄弟讨回场子!</t>
+  </si>
+  <si>
+    <t>赢的会是我,看好了。</t>
+  </si>
+  <si>
+    <t>瞪大眼睛,看谁输谁赢!</t>
+  </si>
+  <si>
+    <t>那今天就轮到猎物翻身。</t>
   </si>
   <si>
     <t>首领面前,你才是猎物!</t>
   </si>
   <si>
-    <t>眼睛再大,也看不到赢。</t>
-  </si>
-  <si>
-    <t>这一眼,看穿你底牌!</t>
-  </si>
-  <si>
-    <t>首领?马上就是前任了。</t>
+    <t>看穿了,你也赢不走。</t>
+  </si>
+  <si>
+    <t>这一眼,就看穿你底牌!</t>
+  </si>
+  <si>
+    <t>掂量完了,你该退位了。</t>
   </si>
   <si>
     <t>大话之前,先掂量掂量!</t>
@@ -1210,8 +1210,8 @@
     <col min="1" max="1" width="6.375" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.20833333333333" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.45833333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="5.325" style="2" customWidth="1"/>
-    <col min="5" max="5" width="5.975" style="2" customWidth="1"/>
+    <col min="4" max="4" width="26.0833333333333" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.5416666666667" style="2" customWidth="1"/>
     <col min="6" max="6" width="13.3583333333333" style="2" customWidth="1"/>
     <col min="7" max="7" width="11.5166666666667" style="2" customWidth="1"/>
     <col min="8" max="8" width="18.0416666666667" style="2" customWidth="1"/>
